--- a/ksoft_old/docs/records/Receipt_Via_Transp_Enum.xlsx
+++ b/ksoft_old/docs/records/Receipt_Via_Transp_Enum.xlsx
@@ -1426,13 +1426,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{938DD44A-886F-49D0-B554-50D22B0B5F22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B7AC3A-1161-490F-AF49-BE0E24176B1F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB405DDA-69EC-44CF-ACA9-4F00671605E5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88764920-358B-49DB-AA86-EB34B41689D8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECDB2095-7F41-4922-B0ED-CD99410C0FA7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{925733FD-20BC-4809-B66D-7DF02C50E4F8}"/>
 </file>
--- a/ksoft_old/docs/records/Receipt_Via_Transp_Enum.xlsx
+++ b/ksoft_old/docs/records/Receipt_Via_Transp_Enum.xlsx
@@ -1426,13 +1426,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B7AC3A-1161-490F-AF49-BE0E24176B1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4CC4E1D-8062-42B8-9B44-F29FC6E37D03}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88764920-358B-49DB-AA86-EB34B41689D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{645EBA4F-6181-41DC-8DCB-47CF492A9E38}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{925733FD-20BC-4809-B66D-7DF02C50E4F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A435030-0713-4C09-8F6C-E486A3C851C1}"/>
 </file>
--- a/ksoft_old/docs/records/Receipt_Via_Transp_Enum.xlsx
+++ b/ksoft_old/docs/records/Receipt_Via_Transp_Enum.xlsx
@@ -1426,13 +1426,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4CC4E1D-8062-42B8-9B44-F29FC6E37D03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{938DD44A-886F-49D0-B554-50D22B0B5F22}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{645EBA4F-6181-41DC-8DCB-47CF492A9E38}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB405DDA-69EC-44CF-ACA9-4F00671605E5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A435030-0713-4C09-8F6C-E486A3C851C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECDB2095-7F41-4922-B0ED-CD99410C0FA7}"/>
 </file>